--- a/walker-ranch-area-apartments.xlsx
+++ b/walker-ranch-area-apartments.xlsx
@@ -9,10 +9,14 @@
   </bookViews>
   <sheets>
     <sheet name="Apartments" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Read Me" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Houses &amp; Townhomes" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Townhome Communities" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Read Me" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Apartments!$A$1:$Q$37</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Houses &amp; Townhomes'!$A$1:$K$50</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Townhome Communities'!$A$1:$L$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="532">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -794,6 +798,708 @@
     <t xml:space="preserve">apartments.com; apartmentratings.com; rentcafe.com</t>
   </si>
   <si>
+    <t xml:space="preserve">Area / Neighborhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sqft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ per Sqft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details / Caveats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14806 Northern Blvd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Blvd off Bitters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Townhome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Townhome strip; cheapest townhome found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments.com; Homes.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7212 Savannah Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13018 Heimer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heimer townhome cluster nr Bitters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Townhome/condo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments.com; HAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1411 Flower Brk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Brook (garden homes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest house found in sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 Shalimar Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castle Hills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget option in Castle Hills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent.com; Homes.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16330 Elk Hollow St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thousand Oaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10622 Mount Ida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homes.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16718 Basin Oak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redfin; Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">543 Dawnview Ln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castle Hills-adjacent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North of Loop 410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829 W Bitters Rd (units)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitters Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small multi-unit / townhome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4BR/2BA unit at $1,875; a separate gated 2BR/2.5BA townhome-style unit at same address also listed (price not shown); near 281/Wurzbach Pkwy/airport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments.com; ApartmentList</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14819 Academy Oak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11813 Petal Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Ave corridor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zip unverified (78216/78213 line)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1411 Brook Mdw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Brook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comp: 1419 Brook Mdw rented at $1,890 - price band corroborated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow; Movoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13710 Chittim Mdw Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Ave/Bitters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16331 Boulder Pass St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326 Beryl Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5403 Argyle Way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14110 Stone Tree St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thousand Oaks (west edge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 Rogers Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pet-friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zumper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16710 Summer Creek Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer Creek/Deerfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEISD; rent varies by site: $2,200 (Zillow) vs $2,350 (Apartments.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow; Apartments.com; HAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15410 Circle Path St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brookwood/Bluffs nr Henderson Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15022 Polynesian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huebner/NW Military</t>
+  </si>
+  <si>
+    <t xml:space="preserve">463 Sprucewood Ln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blanco corridor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surfaced in one snippet only - POSSIBLY STALE, verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow; Homes.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1703 Searcy Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitters/Blanco corridor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2615 Adams Cir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15710 Fern Ridge St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brook Hollow/Heimer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15607 NW Military Hwy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavano Park corridor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House/townhome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117 Danube Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castle Hills area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112 Sunway Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hollywood Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments.com; Rent.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1219 Thrush Rdg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huebner Village/Deerfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2607 Chestnut Bnd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNVERIFIED - snippet only, could not re-confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trulia; Apartments.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Ariana Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gated garden-home enclave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garden home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1719 Eagle Mdw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deerfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEISD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zumper; Rent.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84 Roundup Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castle Hills proper; confirmed active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow; Apartments.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2939 Quail Oak St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137 Antler Cir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big-lot neighborhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116 S Gardenview Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106 Village Cir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hill Country Village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pet-friendly; large lots, NEISD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15038 Polynesian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavano Park-adjacent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132 Wagon Trail Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavano Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEISD, large-lot community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1202 Tranquil Trail Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largest sqft found in sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 Silverhorn Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverhorn (golf course, gated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gated golf-course community off Bitters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForRent; Homes.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15238 Chalet Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chimney Hills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off Bitters/Jones Maltsberger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16615 Raven Glenn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large 2-story; $3,070-$3,100 across sites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1306 Charlisas Way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walker Ranch subdivision (gated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN the Walker Ranch subdivision itself, off Bitters &amp; Blanco; 2-story, 3 living areas, high ceilings, oak trees; MLS 1832284 - may already be leased (listing shows Sold/Residential Lease); an older $2,900 4BR/2.5BA listing at same address also surfaced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zumper; Rent.com; Realty Texas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161 Twinleaf Ln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large mid-century lot; NEISD; confirmed active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow; Compass; Homes.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1303 Bluff Forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bluffs of Inwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homes.com; ForRent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bluffview Greens (address withheld)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off Bitters Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House (furnished)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furnished executive lease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compass; HAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115 Canter Gait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentley Manor/Shavano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beds/Baths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sqft Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also on Apartments Tab?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15083 San Pedro Ave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments + true townhomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-3BR; townhomes 2-3BR/up to 2.5BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722-1,816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From ~$1,233; 1BR $1,579+, 2BR $1,675+, 3BR $1,982+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2/5 Birdeye (75); 4.7/5 AR (168, sub-scores 4.6-4.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only community with attached garages standard on townhome units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newer luxury; dog park/wash, yoga studio, resort pool; gated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ironridgeapartments.com; apartments.com; apartmentratings.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments incl. 2-story townhome-style units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-3BR; townhome layouts 2-3BR/2.5BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503-1,242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From ~$749 (possibly stale); mid-$900s-$1,600s typical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0/5 AR (117 votes); 3.4/5 ForRent (19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closest to Walker Ranch (~0.5 mi); reviews cite maintenance/pest complaints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 1997, 324 units; 2 pools, fitness center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apexsanantonio.com; apartments.com; apartmentratings.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broken Oak Townhomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1935 Broken Oak St</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dedicated townhome community (only 100% townhome community found)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-2BR/1.5-2.5BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,156-1,217 (2BR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1BR ~$749-$945; 2BR ~$1,000-$1,250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed-to-negative, AR (42 reviews)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance and break-in complaints; some praise for quiet/staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 1983, 72 units; Thousand Oaks area; pool, gym, dog park; ~3.5-4 mi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apartmentratings.com; rent.com; apartments.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connemara Estates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2650 Thousand Oaks Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condo-style (4 units/building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-3BR/2-2.5BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1,100-1,500 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2BR ~$1,247-$1,411; 3BR from ~$1,533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed, AR (92) + Yelp (30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Praise for spacious units/grounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5 acres; assigned covered parking; tennis/basketball, pool/spa, 24-hr gym; ~4 mi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apartments.com; apartmentratings.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biltmore Park Apartments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1111 Vista Valet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments + townhome units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-2BR/1-2BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">670-1,032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$787-$2,088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6/5 AR (273 votes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neighborhood sub-score 4.5, staff 4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remodeled interiors; tucked-away location ~1 mi from Walker Ranch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments + townhome floor plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-2BR/1-2.5BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720-1,075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$945-$1,398 (1BR $900+, 2BR $1,131+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8/5 AR (95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Military/teacher discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 1983, 190 units; fireplaces, private patios, pool, dog park; ~3.5 mi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments incl. townhome floor plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~700-1,200 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$955-$1,480 (1BR $955+, 2BR $1,145+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed, AR (88) + Yelp (19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC/mold and fee complaints; some staff praise; 6 weeks free (Jul 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W/D hookups, patios; Thousand Oaks area; ~3.5 mi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostly flats (appears on townhome filter pages)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-3BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~650-1,300 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1BR ~$874-$945; 2BR ~$1,154; 3BR $1,610-$1,674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8/5 AR (203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recent maintenance/staff sub-scores poor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backs to Salado Creek greenway; clubhouse, sauna, resort pool; ~1.5 mi; 1 month free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apartmentratings.com; redfin.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartment/condo-style, some 2-story units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~650-1,100 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$909-$1,449 (from ~$870)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed (no consolidated score)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promo: half off first 2 months (Jul 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 1982, 175 units; in-unit laundry, fireplaces, sports courts, trails; ~1.5 mi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apartments.com; rentcafe.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apartments w/ rentable private garages, house-like finishes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">665-1,313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$911-$1,443 (from ~$971)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive-leaning, AR (64); Birdeye 3.9 (200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gated w/ perimeter fence + in-unit alarms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built 2001, 312 units; near Huebner Oaks/Hardberger Park; ~1.5-2 mi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">escalanteapts.com; apartments.com; apartmentratings.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apartments near Walker Ranch - San Antonio, TX</t>
   </si>
   <si>
@@ -885,18 +1591,53 @@
   </si>
   <si>
     <t xml:space="preserve">Average rating (rated only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houses &amp; Townhomes tab (added 2026-07-24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49 individual houses, townhomes, and garden homes for rent within ~3 miles of Walker Ranch (zips 78216, 78213/Castle Hills, 78232, 78248/Deerfield, 78231/Shavano Park, west edge of 78247/Thousand Oaks), sorted cheapest first. $ per Sqft is computed where both rent and sqft are known - useful for spotting over/under-priced homes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPORTANT - churn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individual listings move in DAYS, not weeks - this tab is a snapshot taken 2026-07-24 from search-index data (listing sites block direct scraping). Verify every listing on the source site before contacting. Rows marked UNVERIFIED or POSSIBLY STALE could not be re-confirmed. One highlight: 1306 Charlisas Way is inside the Walker Ranch subdivision itself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No reviews for houses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private-landlord houses have no review scores. Screen the landlord instead: ask who manages it (owner vs PM company), response time on repairs, and look up the PM company's Google/BBB reviews.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negotiation note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private landlords negotiate more freely than apartment revenue-management software - especially on homes vacant 30+ days. Asking rent on houses is commonly 3-8% above what they will accept.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Townhome Communities tab (added 2026-07-24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 professionally managed communities offering townhome / condo-style units (attached garages, 2-story layouts, private patios). Several also appear on the Apartments tab (flagged in column K) - listed here with their townhome-specific details. Only Broken Oak is 100% townhomes; Ironridge is the only one with attached garages standard.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0"/>
+    <numFmt numFmtId="170" formatCode="\$0.00"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -1013,8 +1754,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1043,6 +1788,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1164,6 +1917,14 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -1350,1758 +2111,1758 @@
   <dimension ref="A1:Q37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>917</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="6" t="n">
         <v>1297</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="6" t="n">
+      <c r="I2" s="5"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="7" t="str">
+      <c r="O2" s="8" t="str">
         <f aca="false">IF(OR(I2="",E2="",E2=0),"",ROUND(I2/(E2/1000),2))</f>
         <v/>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>1075</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="2" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="6" t="n">
+      <c r="I3" s="5"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="7" t="n">
         <v>188</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="7" t="str">
+      <c r="N3" s="4"/>
+      <c r="O3" s="8" t="str">
         <f aca="false">IF(OR(I3="",E3="",E3=0),"",ROUND(I3/(E3/1000),2))</f>
         <v/>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>675</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="2" t="s">
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="2" t="s">
+      <c r="I4" s="5"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="7" t="str">
+      <c r="N4" s="4"/>
+      <c r="O4" s="8" t="str">
         <f aca="false">IF(OR(I4="",E4="",E4=0),"",ROUND(I4/(E4/1000),2))</f>
         <v/>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="P4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>943</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>1303</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>1638</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="7" t="n">
         <v>681</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="7" t="n">
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="8" t="n">
         <f aca="false">IF(OR(I5="",E5="",E5=0),"",ROUND(I5/(E5/1000),2))</f>
         <v>4.45</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="P5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Q5" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>855</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>1215</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="2" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="7" t="n">
+      <c r="N6" s="4"/>
+      <c r="O6" s="8" t="n">
         <f aca="false">IF(OR(I6="",E6="",E6=0),"",ROUND(I6/(E6/1000),2))</f>
         <v>4.91</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>799</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>1400</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="2" t="s">
+      <c r="G7" s="6"/>
+      <c r="H7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="7" t="n">
         <v>141</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="7" t="n">
+      <c r="N7" s="4"/>
+      <c r="O7" s="8" t="n">
         <f aca="false">IF(OR(I7="",E7="",E7=0),"",ROUND(I7/(E7/1000),2))</f>
         <v>3.88</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>769</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>1075</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="2" t="s">
+      <c r="G8" s="6"/>
+      <c r="H8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="6" t="n">
+      <c r="I8" s="5"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="7" t="str">
+      <c r="N8" s="4"/>
+      <c r="O8" s="8" t="str">
         <f aca="false">IF(OR(I8="",E8="",E8=0),"",ROUND(I8/(E8/1000),2))</f>
         <v/>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="P8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>1044</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>1303</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>1608</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="7" t="n">
         <v>298</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="7" t="n">
+      <c r="N9" s="4"/>
+      <c r="O9" s="8" t="n">
         <f aca="false">IF(OR(I9="",E9="",E9=0),"",ROUND(I9/(E9/1000),2))</f>
         <v>4.02</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="P9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="Q9" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>940</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="2" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="7" t="n">
         <v>203</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="7" t="n">
+      <c r="N10" s="4"/>
+      <c r="O10" s="8" t="n">
         <f aca="false">IF(OR(I10="",E10="",E10=0),"",ROUND(I10/(E10/1000),2))</f>
         <v>4.89</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="P10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="Q10" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>850</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="6" t="n">
         <v>1235</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="2" t="s">
+      <c r="G11" s="6"/>
+      <c r="H11" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="2" t="s">
+      <c r="I11" s="5"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="7" t="str">
+      <c r="N11" s="4"/>
+      <c r="O11" s="8" t="str">
         <f aca="false">IF(OR(I11="",E11="",E11=0),"",ROUND(I11/(E11/1000),2))</f>
         <v/>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="P11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="Q11" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="6" t="n">
         <v>1579</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="6" t="n">
         <v>1675</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <v>1982</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="7" t="n">
         <v>168</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="L12" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="7" t="n">
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="8" t="n">
         <f aca="false">IF(OR(I12="",E12="",E12=0),"",ROUND(I12/(E12/1000),2))</f>
         <v>2.98</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="P12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="Q12" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="6" t="n">
         <v>875</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="2" t="s">
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="6" t="n">
+      <c r="I13" s="5"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="L13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="7" t="str">
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="8" t="str">
         <f aca="false">IF(OR(I13="",E13="",E13=0),"",ROUND(I13/(E13/1000),2))</f>
         <v/>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="P13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="Q13" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="6" t="n">
         <v>809</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="6" t="n">
         <v>1154</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="6" t="n">
         <v>1564</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>203</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="L14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="O14" s="7" t="n">
+      <c r="O14" s="8" t="n">
         <f aca="false">IF(OR(I14="",E14="",E14=0),"",ROUND(I14/(E14/1000),2))</f>
         <v>4.7</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="P14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="Q14" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="6" t="n">
         <v>770</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="6" t="n">
         <v>1278</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="2" t="s">
+      <c r="G15" s="6"/>
+      <c r="H15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="6" t="n">
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="L15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="7" t="str">
+      <c r="N15" s="4"/>
+      <c r="O15" s="8" t="str">
         <f aca="false">IF(OR(I15="",E15="",E15=0),"",ROUND(I15/(E15/1000),2))</f>
         <v/>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="P15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="Q15" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="6" t="n">
         <v>827</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="6" t="n">
         <v>1146</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="2" t="s">
+      <c r="G16" s="6"/>
+      <c r="H16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="L16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="M16" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="N16" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="O16" s="7" t="n">
+      <c r="O16" s="8" t="n">
         <f aca="false">IF(OR(I16="",E16="",E16=0),"",ROUND(I16/(E16/1000),2))</f>
         <v>4.11</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="P16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="Q16" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="6" t="n">
         <v>870</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="2" t="s">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="L17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="M17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="7" t="n">
+      <c r="N17" s="4"/>
+      <c r="O17" s="8" t="n">
         <f aca="false">IF(OR(I17="",E17="",E17=0),"",ROUND(I17/(E17/1000),2))</f>
         <v>4.48</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="P17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="Q17" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="6" t="n">
         <v>1060</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="6" t="n">
         <v>1558</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="6" t="n">
         <v>2525</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="7" t="n">
         <v>566</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="L18" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="7" t="n">
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="8" t="n">
         <f aca="false">IF(OR(I18="",E18="",E18=0),"",ROUND(I18/(E18/1000),2))</f>
         <v>4.43</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="P18" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="Q18" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="6" t="n">
         <v>965</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="6" t="n">
         <v>1310</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="6" t="n">
         <v>1835</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K19" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="L19" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="7" t="n">
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="8" t="n">
         <f aca="false">IF(OR(I19="",E19="",E19=0),"",ROUND(I19/(E19/1000),2))</f>
         <v>3.94</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="P19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="Q19" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="6" t="n">
         <v>633</v>
       </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="2" t="s">
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="6" t="n">
+      <c r="I20" s="5"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="L20" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="7" t="str">
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="8" t="str">
         <f aca="false">IF(OR(I20="",E20="",E20=0),"",ROUND(I20/(E20/1000),2))</f>
         <v/>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="P20" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="Q20" s="3" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="6" t="n">
         <v>971</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="6" t="n">
         <v>1418</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="6" t="n">
         <v>1999</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L21" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="7" t="n">
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="8" t="n">
         <f aca="false">IF(OR(I21="",E21="",E21=0),"",ROUND(I21/(E21/1000),2))</f>
         <v>4.02</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="P21" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="Q21" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="6" t="n">
         <v>685</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="6" t="n">
         <v>1025</v>
       </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="2" t="s">
+      <c r="G22" s="6"/>
+      <c r="H22" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K22" s="7" t="n">
         <v>149</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="L22" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="M22" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="7" t="n">
+      <c r="N22" s="4"/>
+      <c r="O22" s="8" t="n">
         <f aca="false">IF(OR(I22="",E22="",E22=0),"",ROUND(I22/(E22/1000),2))</f>
         <v>4.82</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="P22" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="Q22" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="6" t="n">
         <v>499</v>
       </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="2" t="s">
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="K23" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="L23" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="M23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="7" t="n">
+      <c r="N23" s="4"/>
+      <c r="O23" s="8" t="n">
         <f aca="false">IF(OR(I23="",E23="",E23=0),"",ROUND(I23/(E23/1000),2))</f>
         <v>5.41</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="P23" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="Q23" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="6" t="n">
         <v>1017</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="2" t="s">
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="2" t="s">
+      <c r="I24" s="5"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="7" t="str">
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="8" t="str">
         <f aca="false">IF(OR(I24="",E24="",E24=0),"",ROUND(I24/(E24/1000),2))</f>
         <v/>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="P24" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="Q24" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="6" t="n">
         <v>725</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="2" t="s">
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" s="7" t="n">
         <v>317</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="L25" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="M25" s="3" t="s">
+      <c r="M25" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="7" t="n">
+      <c r="N25" s="4"/>
+      <c r="O25" s="8" t="n">
         <f aca="false">IF(OR(I25="",E25="",E25=0),"",ROUND(I25/(E25/1000),2))</f>
         <v>4.28</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="P25" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="Q25" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="6" t="n">
         <v>1175</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="2" t="s">
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I26" s="4"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="6" t="n">
+      <c r="I26" s="5"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="L26" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="7" t="str">
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="8" t="str">
         <f aca="false">IF(OR(I26="",E26="",E26=0),"",ROUND(I26/(E26/1000),2))</f>
         <v/>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="P26" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="Q26" s="2" t="s">
+      <c r="Q26" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="6" t="n">
         <v>665</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="6" t="n">
         <v>895</v>
       </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="2" t="s">
+      <c r="G27" s="6"/>
+      <c r="H27" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="2" t="s">
+      <c r="I27" s="5"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="M27" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="N27" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="O27" s="7" t="str">
+      <c r="O27" s="8" t="str">
         <f aca="false">IF(OR(I27="",E27="",E27=0),"",ROUND(I27/(E27/1000),2))</f>
         <v/>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="P27" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="Q27" s="2" t="s">
+      <c r="Q27" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="6" t="n">
         <v>1016</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="6" t="n">
         <v>1690</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="G28" s="6" t="n">
         <v>2045</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="K28" s="7" t="n">
         <v>272</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="L28" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="M28" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="7" t="n">
+      <c r="N28" s="4"/>
+      <c r="O28" s="8" t="n">
         <f aca="false">IF(OR(I28="",E28="",E28=0),"",ROUND(I28/(E28/1000),2))</f>
         <v>3.74</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="P28" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="Q28" s="2" t="s">
+      <c r="Q28" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="6" t="n">
         <v>810</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="6" t="n">
         <v>1075</v>
       </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="2" t="s">
+      <c r="G29" s="6"/>
+      <c r="H29" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="I29" s="4"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="2" t="s">
+      <c r="I29" s="5"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="M29" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="7" t="str">
+      <c r="N29" s="4"/>
+      <c r="O29" s="8" t="str">
         <f aca="false">IF(OR(I29="",E29="",E29=0),"",ROUND(I29/(E29/1000),2))</f>
         <v/>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="P29" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="Q29" s="2" t="s">
+      <c r="Q29" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="6" t="n">
         <v>990</v>
       </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="2" t="s">
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="2" t="s">
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="M30" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="N30" s="3"/>
-      <c r="O30" s="7" t="str">
+      <c r="N30" s="4"/>
+      <c r="O30" s="8" t="str">
         <f aca="false">IF(OR(I30="",E30="",E30=0),"",ROUND(I30/(E30/1000),2))</f>
         <v/>
       </c>
-      <c r="P30" s="2" t="s">
+      <c r="P30" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="Q30" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="6" t="n">
         <v>683</v>
       </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="2" t="s">
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="K31" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="L31" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3" t="s">
+      <c r="M31" s="4"/>
+      <c r="N31" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="O31" s="7" t="n">
+      <c r="O31" s="8" t="n">
         <f aca="false">IF(OR(I31="",E31="",E31=0),"",ROUND(I31/(E31/1000),2))</f>
         <v>3.66</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="P31" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="Q31" s="2" t="s">
+      <c r="Q31" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="6" t="n">
         <v>849</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="6" t="n">
         <v>1230</v>
       </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="2" t="s">
+      <c r="G32" s="6"/>
+      <c r="H32" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="6" t="n">
+      <c r="I32" s="5"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="L32" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="7" t="str">
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="8" t="str">
         <f aca="false">IF(OR(I32="",E32="",E32=0),"",ROUND(I32/(E32/1000),2))</f>
         <v/>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="P32" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="Q32" s="2" t="s">
+      <c r="Q32" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="6" t="n">
         <v>740</v>
       </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="2" t="s">
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I33" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="K33" s="7" t="n">
         <v>143</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="L33" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="7" t="n">
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="8" t="n">
         <f aca="false">IF(OR(I33="",E33="",E33=0),"",ROUND(I33/(E33/1000),2))</f>
         <v>3.38</v>
       </c>
-      <c r="P33" s="2" t="s">
+      <c r="P33" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="Q33" s="2" t="s">
+      <c r="Q33" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="6" t="n">
         <v>1006</v>
       </c>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="2" t="s">
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I34" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J34" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K34" s="6" t="n">
+      <c r="K34" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="L34" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="M34" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N34" s="3"/>
-      <c r="O34" s="7" t="n">
+      <c r="N34" s="4"/>
+      <c r="O34" s="8" t="n">
         <f aca="false">IF(OR(I34="",E34="",E34=0),"",ROUND(I34/(E34/1000),2))</f>
         <v>2.78</v>
       </c>
-      <c r="P34" s="2" t="s">
+      <c r="P34" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="Q34" s="2" t="s">
+      <c r="Q34" s="3" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="6" t="n">
         <v>762</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="6" t="n">
         <v>930</v>
       </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="2" t="s">
+      <c r="G35" s="6"/>
+      <c r="H35" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="I35" s="4"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="6" t="n">
+      <c r="I35" s="5"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="L35" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3" t="s">
+      <c r="M35" s="4"/>
+      <c r="N35" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O35" s="7" t="str">
+      <c r="O35" s="8" t="str">
         <f aca="false">IF(OR(I35="",E35="",E35=0),"",ROUND(I35/(E35/1000),2))</f>
         <v/>
       </c>
-      <c r="P35" s="2" t="s">
+      <c r="P35" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="Q35" s="2" t="s">
+      <c r="Q35" s="3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="6" t="n">
         <v>899</v>
       </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="2" t="s">
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="I36" s="4"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="2" t="s">
+      <c r="I36" s="5"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="7" t="str">
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="8" t="str">
         <f aca="false">IF(OR(I36="",E36="",E36=0),"",ROUND(I36/(E36/1000),2))</f>
         <v/>
       </c>
-      <c r="P36" s="2" t="s">
+      <c r="P36" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="Q36" s="2" t="s">
+      <c r="Q36" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="6" t="n">
         <v>678</v>
       </c>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="2" t="s">
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="6" t="n">
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="L37" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3" t="s">
+      <c r="M37" s="4"/>
+      <c r="N37" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O37" s="7" t="str">
+      <c r="O37" s="8" t="str">
         <f aca="false">IF(OR(I37="",E37="",E37=0),"",ROUND(I37/(E37/1000),2))</f>
         <v/>
       </c>
-      <c r="P37" s="2" t="s">
+      <c r="P37" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="Q37" s="2" t="s">
+      <c r="Q37" s="3" t="s">
         <v>255</v>
       </c>
     </row>
@@ -3123,189 +3884,2428 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>256</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="9" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I2" s="10" t="str">
+        <f aca="false">IF(OR(H2="",G2="",G2=0),"",ROUND(H2/G2,2))</f>
+        <v/>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>1344</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>1699</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <f aca="false">IF(OR(H3="",G3="",G3=0),"",ROUND(H3/G3,2))</f>
+        <v>1.26</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="9" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I4" s="10" t="str">
+        <f aca="false">IF(OR(H4="",G4="",G4=0),"",ROUND(H4/G4,2))</f>
+        <v/>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1389</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <f aca="false">IF(OR(H5="",G5="",G5=0),"",ROUND(H5/G5,2))</f>
+        <v>1.26</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>1333</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>1790</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <f aca="false">IF(OR(H6="",G6="",G6=0),"",ROUND(H6/G6,2))</f>
+        <v>1.34</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9" t="n">
+        <v>1795</v>
+      </c>
+      <c r="I7" s="10" t="str">
+        <f aca="false">IF(OR(H7="",G7="",G7=0),"",ROUND(H7/G7,2))</f>
+        <v/>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1285</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <f aca="false">IF(OR(H8="",G8="",G8=0),"",ROUND(H8/G8,2))</f>
+        <v>1.4</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1733</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <f aca="false">IF(OR(H9="",G9="",G9=0),"",ROUND(H9/G9,2))</f>
+        <v>1.04</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1473</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1850</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <f aca="false">IF(OR(H10="",G10="",G10=0),"",ROUND(H10/G10,2))</f>
+        <v>1.26</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1684</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>1875</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <f aca="false">IF(OR(H11="",G11="",G11=0),"",ROUND(H11/G11,2))</f>
+        <v>1.11</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1641</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1875</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <f aca="false">IF(OR(H12="",G12="",G12=0),"",ROUND(H12/G12,2))</f>
+        <v>1.14</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="I13" s="10" t="str">
+        <f aca="false">IF(OR(H13="",G13="",G13=0),"",ROUND(H13/G13,2))</f>
+        <v/>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1448</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <f aca="false">IF(OR(H14="",G14="",G14=0),"",ROUND(H14/G14,2))</f>
+        <v>1.31</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="9" t="n">
+        <v>1965</v>
+      </c>
+      <c r="I15" s="10" t="str">
+        <f aca="false">IF(OR(H15="",G15="",G15=0),"",ROUND(H15/G15,2))</f>
+        <v/>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="9" t="n">
+        <v>1995</v>
+      </c>
+      <c r="I16" s="10" t="str">
+        <f aca="false">IF(OR(H16="",G16="",G16=0),"",ROUND(H16/G16,2))</f>
+        <v/>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>1317</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <f aca="false">IF(OR(H17="",G17="",G17=0),"",ROUND(H17/G17,2))</f>
+        <v>1.59</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>2152</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>2150</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <f aca="false">IF(OR(H18="",G18="",G18=0),"",ROUND(H18/G18,2))</f>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1640</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>2199</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <f aca="false">IF(OR(H19="",G19="",G19=0),"",ROUND(H19/G19,2))</f>
+        <v>1.34</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I20" s="10" t="str">
+        <f aca="false">IF(OR(H20="",G20="",G20=0),"",ROUND(H20/G20,2))</f>
+        <v/>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>1757</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <f aca="false">IF(OR(H21="",G21="",G21=0),"",ROUND(H21/G21,2))</f>
+        <v>1.25</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>2054</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>2295</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <f aca="false">IF(OR(H22="",G22="",G22=0),"",ROUND(H22/G22,2))</f>
+        <v>1.12</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="9" t="n">
+        <v>2295</v>
+      </c>
+      <c r="I23" s="10" t="str">
+        <f aca="false">IF(OR(H23="",G23="",G23=0),"",ROUND(H23/G23,2))</f>
+        <v/>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <f aca="false">IF(OR(H24="",G24="",G24=0),"",ROUND(H24/G24,2))</f>
+        <v>1.28</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>1748</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <f aca="false">IF(OR(H25="",G25="",G25=0),"",ROUND(H25/G25,2))</f>
+        <v>1.32</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>1839</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>2345</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <f aca="false">IF(OR(H26="",G26="",G26=0),"",ROUND(H26/G26,2))</f>
+        <v>1.28</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="9" t="n">
+        <v>2345</v>
+      </c>
+      <c r="I27" s="10" t="str">
+        <f aca="false">IF(OR(H27="",G27="",G27=0),"",ROUND(H27/G27,2))</f>
+        <v/>
+      </c>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="9" t="n">
+        <v>2350</v>
+      </c>
+      <c r="I28" s="10" t="str">
+        <f aca="false">IF(OR(H28="",G28="",G28=0),"",ROUND(H28/G28,2))</f>
+        <v/>
+      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>2034</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <f aca="false">IF(OR(H29="",G29="",G29=0),"",ROUND(H29/G29,2))</f>
+        <v>1.18</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I30" s="10" t="str">
+        <f aca="false">IF(OR(H30="",G30="",G30=0),"",ROUND(H30/G30,2))</f>
+        <v/>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>1909</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <f aca="false">IF(OR(H31="",G31="",G31=0),"",ROUND(H31/G31,2))</f>
+        <v>1.26</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>2223</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>2450</v>
+      </c>
+      <c r="I32" s="10" t="n">
+        <f aca="false">IF(OR(H32="",G32="",G32=0),"",ROUND(H32/G32,2))</f>
+        <v>1.1</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>1786</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>2450</v>
+      </c>
+      <c r="I33" s="10" t="n">
+        <f aca="false">IF(OR(H33="",G33="",G33=0),"",ROUND(H33/G33,2))</f>
+        <v>1.37</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="9" t="n">
+        <v>2475</v>
+      </c>
+      <c r="I34" s="10" t="str">
+        <f aca="false">IF(OR(H34="",G34="",G34=0),"",ROUND(H34/G34,2))</f>
+        <v/>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>2227</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <f aca="false">IF(OR(H35="",G35="",G35=0),"",ROUND(H35/G35,2))</f>
+        <v>1.12</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>1784</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I36" s="10" t="n">
+        <f aca="false">IF(OR(H36="",G36="",G36=0),"",ROUND(H36/G36,2))</f>
+        <v>1.4</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="7"/>
+      <c r="H37" s="9" t="n">
+        <v>2600</v>
+      </c>
+      <c r="I37" s="10" t="str">
+        <f aca="false">IF(OR(H37="",G37="",G37=0),"",ROUND(H37/G37,2))</f>
+        <v/>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2831</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I38" s="10" t="n">
+        <f aca="false">IF(OR(H38="",G38="",G38=0),"",ROUND(H38/G38,2))</f>
+        <v>0.95</v>
+      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>2157</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <f aca="false">IF(OR(H39="",G39="",G39=0),"",ROUND(H39/G39,2))</f>
+        <v>1.25</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2480</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>2790</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <f aca="false">IF(OR(H40="",G40="",G40=0),"",ROUND(H40/G40,2))</f>
+        <v>1.13</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>2629</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>2850</v>
+      </c>
+      <c r="I41" s="10" t="n">
+        <f aca="false">IF(OR(H41="",G41="",G41=0),"",ROUND(H41/G41,2))</f>
+        <v>1.08</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>3033</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>2990</v>
+      </c>
+      <c r="I42" s="10" t="n">
+        <f aca="false">IF(OR(H42="",G42="",G42=0),"",ROUND(H42/G42,2))</f>
+        <v>0.99</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="7"/>
+      <c r="H43" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I43" s="10" t="str">
+        <f aca="false">IF(OR(H43="",G43="",G43=0),"",ROUND(H43/G43,2))</f>
+        <v/>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>2038</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I44" s="10" t="n">
+        <f aca="false">IF(OR(H44="",G44="",G44=0),"",ROUND(H44/G44,2))</f>
+        <v>1.47</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>3028</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>3070</v>
+      </c>
+      <c r="I45" s="10" t="n">
+        <f aca="false">IF(OR(H45="",G45="",G45=0),"",ROUND(H45/G45,2))</f>
+        <v>1.01</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>3211</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>3195</v>
+      </c>
+      <c r="I46" s="10" t="n">
+        <f aca="false">IF(OR(H46="",G46="",G46=0),"",ROUND(H46/G46,2))</f>
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>2941</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I47" s="10" t="n">
+        <f aca="false">IF(OR(H47="",G47="",G47=0),"",ROUND(H47/G47,2))</f>
+        <v>1.16</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="7"/>
+      <c r="H48" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I48" s="10" t="str">
+        <f aca="false">IF(OR(H48="",G48="",G48=0),"",ROUND(H48/G48,2))</f>
+        <v/>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G49" s="7"/>
+      <c r="H49" s="9" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I49" s="10" t="str">
+        <f aca="false">IF(OR(H49="",G49="",G49=0),"",ROUND(H49/G49,2))</f>
+        <v/>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="7"/>
+      <c r="H50" s="9" t="n">
+        <v>4250</v>
+      </c>
+      <c r="I50" s="10" t="str">
+        <f aca="false">IF(OR(H50="",G50="",G50=0),"",ROUND(H50/G50,2))</f>
+        <v/>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K50"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>258</v>
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>260</v>
+      <c r="A4" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>261</v>
+      <c r="A6" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="A7" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L11"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="B8" s="12" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="B9" s="12" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="B10" s="12" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="B11" s="12" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="B22" s="9" t="n">
+      <c r="B12" s="12" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B22" s="12" t="n">
         <f aca="false">COUNTA(Apartments!A2:A37)</f>
         <v>36</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="B23" s="11" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="B23" s="14" t="n">
         <f aca="false">MIN(Apartments!E2:E37)</f>
         <v>499</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="B24" s="11" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="B24" s="14" t="n">
         <f aca="false">MAX(Apartments!E2:E37)</f>
         <v>1579</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B25" s="11" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="B25" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(Apartments!E2:E37),0)</f>
         <v>873</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="B26" s="12" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="B26" s="15" t="n">
         <f aca="false">MAX(Apartments!I2:I37)</f>
         <v>4.7</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="B27" s="12" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="B27" s="15" t="n">
         <f aca="false">ROUND(AVERAGE(Apartments!I2:I37),2)</f>
         <v>3.64</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
